--- a/docs/요구사항_검증표.xlsx
+++ b/docs/요구사항_검증표.xlsx
@@ -13,7 +13,7 @@
     <sheet name="비기능·기타" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'기능 요구사항'!$A$1:$H$74</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'기능 요구사항'!$A$1:$H$75</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">비기능·기타!$A$1:$H$23</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="498">
   <si>
     <r>
       <rPr>
@@ -152,6 +152,79 @@
     <t xml:space="preserve">2026-07-13</t>
   </si>
   <si>
+    <t xml:space="preserve">최종 갱신</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-07-13 — </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">생성 재시도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">폴백</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">피드백 루프 금지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">파일 컨텍스트 선별 반영</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">검증 기준</t>
   </si>
   <si>
@@ -289,6 +362,23 @@
         <rFont val="나눔고딕"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">컨텍스트 오염 검사</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">코드 검토</t>
     </r>
   </si>
@@ -2415,6 +2505,74 @@
       </rPr>
       <t xml:space="preserve">규칙 기반 폴백 이중화</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">무효 구성</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">순환 등</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">시 자동 재시도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">설계 프롬프트에 피드백 루프 금지 규칙</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">F2-106</t>
@@ -2444,6 +2602,33 @@
     <t xml:space="preserve">server 422 detail</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">재시도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">폴백 도입 후에는 생성 실패 자체가 사용자에게 노출되지 않음</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">F2-201</t>
   </si>
   <si>
@@ -4062,6 +4247,182 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">확인</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">추가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">-4</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">작업 관련 파일 선별</t>
+  </si>
+  <si>
+    <t xml:space="preserve">허용 폴더 중 작업과 관련된 파일만 컨텍스트에 포함</t>
+  </si>
+  <si>
+    <t xml:space="preserve">worker/agent/executor.py</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">실측 — 이력서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">여행메모 혼재 폴더에서 자소서 생성 시 여행 표현 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">종 불검출</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, 4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">개 에이전트 전부 이력서만 선택</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">요구사항 외 추가 구현</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">무관한 개인 파일이 결과물에 섞이는 컨텍스트 오염 방지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">선별도 로컬 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LLM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">으로 수행</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="나눔고딕"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">프라이버시 유지</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
     </r>
   </si>
   <si>
@@ -6904,47 +7265,55 @@
         <v>9</v>
       </c>
     </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C12" s="7" t="n">
-        <f aca="false">COUNTIF('기능 요구사항'!$E$2:$E$74,"구현 완료")</f>
-        <v>65</v>
+        <f aca="false">COUNTIF('기능 요구사항'!$E$2:$E$75,"구현 완료")</f>
+        <v>66</v>
       </c>
       <c r="D12" s="7" t="n">
-        <f aca="false">COUNTIF('기능 요구사항'!$E$2:$E$74,"부분 구현")</f>
+        <f aca="false">COUNTIF('기능 요구사항'!$E$2:$E$75,"부분 구현")</f>
         <v>7</v>
       </c>
       <c r="E12" s="7" t="n">
-        <f aca="false">COUNTIF('기능 요구사항'!$E$2:$E$74,"미구현")</f>
+        <f aca="false">COUNTIF('기능 요구사항'!$E$2:$E$75,"미구현")</f>
         <v>1</v>
       </c>
       <c r="F12" s="8" t="n">
         <f aca="false">SUM(C12:E12)</f>
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C13" s="7" t="n">
         <f aca="false">COUNTIF(비기능·기타!$E$2:$E$23,"구현 완료")</f>
@@ -6965,11 +7334,11 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C14" s="10" t="n">
         <f aca="false">SUM(C12:C13)</f>
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D14" s="10" t="n">
         <f aca="false">SUM(D12:D13)</f>
@@ -6981,45 +7350,45 @@
       </c>
       <c r="F14" s="10" t="n">
         <f aca="false">SUM(F12:F13)</f>
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C16" s="11" t="n">
         <f aca="false">C14/F14</f>
-        <v>0.821052631578947</v>
+        <v>0.822916666666667</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="14" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="15" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -7038,7 +7407,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr defaultColWidth="7.2421875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.02"/>
@@ -7053,1856 +7422,1884 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H2" s="17"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>35</v>
-      </c>
       <c r="G3" s="19" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H3" s="19"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C4" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="G4" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="G4" s="19" t="s">
-        <v>40</v>
-      </c>
       <c r="H4" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G7" s="19" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H7" s="19"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H8" s="19"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="16" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H9" s="17"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G10" s="19" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H10" s="19"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G11" s="19" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H11" s="19" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G12" s="19" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H12" s="19"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G13" s="19" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H13" s="19" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="16" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G14" s="18" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H14" s="17"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="19" t="s">
-        <v>91</v>
-      </c>
       <c r="G15" s="6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H16" s="19" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G17" s="19" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G19" s="19" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H19" s="19" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G20" s="19" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G21" s="19" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H21" s="19"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="16" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H22" s="17" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="B23" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" s="19" t="s">
-        <v>133</v>
-      </c>
       <c r="G23" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H23" s="19"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G24" s="19" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F25" s="19" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F26" s="19" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="16" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F27" s="17" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H27" s="17"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C28" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="D28" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="E28" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" s="19" t="s">
-        <v>156</v>
-      </c>
       <c r="G28" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H28" s="19"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F29" s="19" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G29" s="19" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H29" s="19" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F30" s="19" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H30" s="19"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F31" s="19" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H31" s="19" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F32" s="19" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F33" s="19" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G33" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="H33" s="19"/>
+        <v>42</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="16" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B34" s="17" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F34" s="17" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G34" s="18" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="H34" s="17"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F35" s="19" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H35" s="19"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="H37" s="19"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D38" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="E38" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F38" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="E38" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>202</v>
-      </c>
       <c r="G38" s="6" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="G39" s="19" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="H39" s="19" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H40" s="19"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H41" s="19"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B42" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="E42" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" s="19" t="s">
         <v>185</v>
       </c>
-      <c r="C42" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="E42" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F42" s="19" t="s">
-        <v>183</v>
-      </c>
       <c r="G42" s="19" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H42" s="19"/>
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="20" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="20" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F44" s="19" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="16" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B45" s="17" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C45" s="18" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D45" s="18" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F45" s="17" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="G45" s="18" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H45" s="17"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="7" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B46" s="19" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D46" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="E46" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F46" s="19" t="s">
         <v>242</v>
       </c>
-      <c r="E46" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F46" s="19" t="s">
-        <v>239</v>
-      </c>
       <c r="G46" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H46" s="19"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="7" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B47" s="19" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F47" s="19" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="G47" s="19" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="H47" s="19"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B48" s="19" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="7" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B49" s="19" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F49" s="19" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="G49" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H49" s="19"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="7" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B50" s="19" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G50" s="19" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H50" s="19"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="16" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B51" s="17" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C51" s="18" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D51" s="18" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F51" s="17" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="G51" s="17" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="H51" s="17"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="7" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B52" s="19" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F52" s="19" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="H52" s="19" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="7" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B53" s="19" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F53" s="19" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="G53" s="6" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="H53" s="19"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="7" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="E54" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F54" s="19" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G54" s="19" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="E55" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F55" s="19" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="G55" s="6" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="H55" s="19"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="7" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="E56" s="14" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="7" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="E57" s="14" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F57" s="19" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="G57" s="19" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="7" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F58" s="19" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="H58" s="19" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="7" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B59" s="19" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F59" s="19" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="H59" s="19" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="7" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F60" s="19" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="H60" s="19" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="7" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B61" s="19" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E61" s="14" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H61" s="19" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="7" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B62" s="19" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="H62" s="19"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="16" t="s">
-        <v>327</v>
-      </c>
-      <c r="B63" s="17" t="s">
-        <v>328</v>
-      </c>
-      <c r="C63" s="18" t="s">
-        <v>329</v>
-      </c>
-      <c r="D63" s="18" t="s">
+    <row r="63" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="20" t="s">
         <v>330</v>
       </c>
+      <c r="B63" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>332</v>
+      </c>
       <c r="E63" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F63" s="18" t="s">
-        <v>331</v>
-      </c>
-      <c r="G63" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="H63" s="17"/>
+        <v>13</v>
+      </c>
+      <c r="F63" s="19" t="s">
+        <v>333</v>
+      </c>
+      <c r="G63" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="H63" s="6" t="s">
+        <v>335</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="7" t="s">
-        <v>332</v>
-      </c>
-      <c r="B64" s="19" t="s">
-        <v>328</v>
-      </c>
-      <c r="C64" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="D64" s="6" t="s">
-        <v>334</v>
+      <c r="A64" s="16" t="s">
+        <v>336</v>
+      </c>
+      <c r="B64" s="17" t="s">
+        <v>337</v>
+      </c>
+      <c r="C64" s="18" t="s">
+        <v>338</v>
+      </c>
+      <c r="D64" s="18" t="s">
+        <v>339</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F64" s="19" t="s">
-        <v>335</v>
-      </c>
-      <c r="G64" s="19" t="s">
-        <v>336</v>
-      </c>
-      <c r="H64" s="19"/>
+        <v>13</v>
+      </c>
+      <c r="F64" s="18" t="s">
+        <v>340</v>
+      </c>
+      <c r="G64" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="H64" s="17"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="B65" s="19" t="s">
         <v>337</v>
       </c>
-      <c r="B65" s="19" t="s">
-        <v>328</v>
-      </c>
       <c r="C65" s="6" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F65" s="19" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="G65" s="19" t="s">
-        <v>341</v>
-      </c>
-      <c r="H65" s="6" t="s">
-        <v>342</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="H65" s="19"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="7" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B66" s="19" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F66" s="19" t="s">
-        <v>346</v>
-      </c>
-      <c r="G66" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="H66" s="19"/>
+        <v>349</v>
+      </c>
+      <c r="G66" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>351</v>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="7" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B67" s="19" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F67" s="19" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="G67" s="6" t="s">
-        <v>68</v>
+        <v>356</v>
       </c>
       <c r="H67" s="19"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="20" t="s">
-        <v>352</v>
+      <c r="A68" s="7" t="s">
+        <v>357</v>
       </c>
       <c r="B68" s="19" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="E68" s="14" t="s">
-        <v>12</v>
+        <v>359</v>
+      </c>
+      <c r="E68" s="12" t="s">
+        <v>13</v>
       </c>
       <c r="F68" s="19" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>356</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="H68" s="19"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="16" t="s">
-        <v>357</v>
-      </c>
-      <c r="B69" s="17" t="s">
-        <v>358</v>
-      </c>
-      <c r="C69" s="18" t="s">
-        <v>359</v>
-      </c>
-      <c r="D69" s="18" t="s">
-        <v>360</v>
-      </c>
-      <c r="E69" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F69" s="17" t="s">
+      <c r="A69" s="20" t="s">
         <v>361</v>
       </c>
-      <c r="G69" s="17" t="s">
+      <c r="B69" s="19" t="s">
+        <v>337</v>
+      </c>
+      <c r="C69" s="6" t="s">
         <v>362</v>
       </c>
-      <c r="H69" s="17"/>
+      <c r="D69" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="E69" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F69" s="19" t="s">
+        <v>364</v>
+      </c>
+      <c r="G69" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="H69" s="6" t="s">
+        <v>365</v>
+      </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="B70" s="19" t="s">
-        <v>358</v>
-      </c>
-      <c r="C70" s="6" t="s">
-        <v>364</v>
-      </c>
-      <c r="D70" s="6" t="s">
-        <v>365</v>
+      <c r="A70" s="16" t="s">
+        <v>366</v>
+      </c>
+      <c r="B70" s="17" t="s">
+        <v>367</v>
+      </c>
+      <c r="C70" s="18" t="s">
+        <v>368</v>
+      </c>
+      <c r="D70" s="18" t="s">
+        <v>369</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F70" s="19" t="s">
-        <v>366</v>
-      </c>
-      <c r="G70" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>367</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="F70" s="17" t="s">
+        <v>370</v>
+      </c>
+      <c r="G70" s="17" t="s">
+        <v>371</v>
+      </c>
+      <c r="H70" s="17"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="7" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="B71" s="19" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="E71" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F71" s="19" t="s">
-        <v>371</v>
-      </c>
-      <c r="G71" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="H71" s="19"/>
+        <v>375</v>
+      </c>
+      <c r="G71" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="H71" s="6" t="s">
+        <v>376</v>
+      </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="7" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="B72" s="19" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="E72" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F72" s="19" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H72" s="19"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="7" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="B73" s="19" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>338</v>
+        <v>382</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="E73" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F73" s="19" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="G73" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H73" s="19"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="7" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="B74" s="19" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>380</v>
+        <v>347</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="E74" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F74" s="19" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="H74" s="19" t="s">
-        <v>383</v>
+        <v>70</v>
+      </c>
+      <c r="H74" s="19"/>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="B75" s="19" t="s">
+        <v>367</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="E75" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F75" s="19" t="s">
+        <v>391</v>
+      </c>
+      <c r="G75" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="H75" s="19" t="s">
+        <v>392</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H74"/>
+  <autoFilter ref="A1:H75"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -8934,582 +9331,582 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="B2" s="18" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="G2" s="18" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="H2" s="18" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="H3" s="19"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="H4" s="19"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="H5" s="19"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H7" s="17"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H8" s="19"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G11" s="19" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G13" s="19" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H13" s="19" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="16" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="G15" s="18" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="H15" s="17"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H16" s="19"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>454</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>445</v>
-      </c>
       <c r="C17" s="6" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="G17" s="19" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H17" s="19"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="H18" s="19"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G21" s="19" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H21" s="19" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="16" t="s">
-        <v>477</v>
+        <v>486</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>482</v>
+        <v>491</v>
       </c>
       <c r="H22" s="17" t="s">
-        <v>483</v>
+        <v>492</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="G23" s="19" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>488</v>
+        <v>497</v>
       </c>
     </row>
   </sheetData>
